--- a/Clean_Grievance_Sample.xlsx
+++ b/Clean_Grievance_Sample.xlsx
@@ -140,28 +140,28 @@
     <t>Question</t>
   </si>
   <si>
-    <t>You had lodged a complaint for?</t>
+    <t>What was the reason behind your complaint?</t>
   </si>
   <si>
     <t>Who did you lodge a complaint with?</t>
   </si>
   <si>
-    <t>Were you contacted by the Organization to address your complaint?</t>
+    <t>Did anyone contact you?</t>
   </si>
   <si>
-    <t>Was your complaint/grievance addressed?</t>
+    <t>Was your complaint addressed?</t>
   </si>
   <si>
-    <t>Are you satisfied with the redressal of your complaint?</t>
+    <t>Are you satisfied with the response you received?</t>
   </si>
   <si>
-    <t>Did you lodge complaint again?</t>
+    <t>Did you complain again?</t>
   </si>
   <si>
-    <t>Why didn't you lodge a complaint again?</t>
+    <t>Why didn't you complain again?</t>
   </si>
   <si>
-    <t>What was the outcome of lodging complaint again?</t>
+    <t>What was the outcome of complaining again?</t>
   </si>
 </sst>
 </file>

--- a/Clean_Grievance_Sample.xlsx
+++ b/Clean_Grievance_Sample.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="46">
   <si>
     <t>PROVINCE</t>
   </si>
@@ -794,7 +794,7 @@
       <c r="E15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -997,8 +997,14 @@
       <c r="E25" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>11</v>
+      <c r="F25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">

--- a/Clean_Grievance_Sample.xlsx
+++ b/Clean_Grievance_Sample.xlsx
@@ -59,9 +59,6 @@
     <t>c</t>
   </si>
   <si>
-    <t>e</t>
-  </si>
-  <si>
     <t>Balochistan</t>
   </si>
   <si>
@@ -72,6 +69,9 @@
   </si>
   <si>
     <t>Sindh</t>
+  </si>
+  <si>
+    <t>e</t>
   </si>
   <si>
     <t>Options</t>
@@ -565,8 +565,8 @@
       <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
+      <c r="C4" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>10</v>
@@ -582,8 +582,8 @@
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>14</v>
+      <c r="B5" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
@@ -600,7 +600,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>10</v>
@@ -620,13 +620,13 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>13</v>
+      <c r="C7" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>10</v>
@@ -640,10 +640,10 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>11</v>
@@ -660,7 +660,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>10</v>
@@ -680,7 +680,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>11</v>
@@ -702,8 +702,8 @@
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>10</v>
+      <c r="B11" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>13</v>
@@ -715,12 +715,12 @@
         <v>10</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>11</v>
@@ -740,10 +740,10 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>13</v>
@@ -760,7 +760,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>11</v>
@@ -800,7 +800,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>10</v>
@@ -815,12 +815,12 @@
         <v>10</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>11</v>
@@ -860,7 +860,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>11</v>
@@ -880,7 +880,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>10</v>
@@ -903,7 +903,7 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>11</v>
@@ -918,12 +918,12 @@
         <v>10</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>10</v>
@@ -943,10 +943,10 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>10</v>
+      <c r="B23" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>11</v>
@@ -963,10 +963,10 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>14</v>
+      <c r="B24" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>10</v>
@@ -986,7 +986,7 @@
         <v>9</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>10</v>
@@ -1004,7 +1004,7 @@
         <v>10</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -1029,13 +1029,13 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>10</v>
@@ -1049,10 +1049,10 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>10</v>
@@ -1069,10 +1069,10 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>14</v>
+      <c r="B29" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>11</v>
@@ -1089,13 +1089,13 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="B30" s="4" t="s">
         <v>13</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>10</v>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>10</v>
@@ -6122,7 +6122,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>34</v>
@@ -6140,7 +6140,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>35</v>
